--- a/case-studies/kestrel-valley-cycle/data/quickbooks/Journal.xlsx
+++ b/case-studies/kestrel-valley-cycle/data/quickbooks/Journal.xlsx
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="H24" s="1" t="n">
-        <v>3073.93</v>
+        <v>2878.85</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -954,15 +954,15 @@
         </is>
       </c>
       <c r="I25" s="1" t="n">
-        <v>3073.93</v>
+        <v>2878.85</v>
       </c>
     </row>
     <row r="26">
       <c r="H26" s="1" t="n">
-        <v>3073.93</v>
+        <v>2878.85</v>
       </c>
       <c r="I26" s="1" t="n">
-        <v>3073.93</v>
+        <v>2878.85</v>
       </c>
     </row>
     <row r="27">
@@ -1127,8 +1127,8 @@
           <t>67000 Office Supplies</t>
         </is>
       </c>
-      <c r="I34" s="1" t="n">
-        <v>714</v>
+      <c r="H34" s="1" t="n">
+        <v>169.33</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
           <t>20000 Accounts Payable (A/P)</t>
         </is>
       </c>
-      <c r="H35" s="1" t="n">
-        <v>714</v>
+      <c r="I35" s="1" t="n">
+        <v>169.33</v>
       </c>
     </row>
     <row r="36">
       <c r="H36" s="1" t="n">
-        <v>714</v>
+        <v>169.33</v>
       </c>
       <c r="I36" s="1" t="n">
-        <v>714</v>
+        <v>169.33</v>
       </c>
     </row>
     <row r="37">
@@ -1856,8 +1856,8 @@
           <t>20000 Accounts Payable (A/P)</t>
         </is>
       </c>
-      <c r="I70" s="1" t="n">
-        <v>722.09</v>
+      <c r="H70" s="1" t="n">
+        <v>241.55</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
@@ -1877,16 +1877,16 @@
           <t>10100 Checking - First Prairie</t>
         </is>
       </c>
-      <c r="H71" s="1" t="n">
-        <v>722.09</v>
+      <c r="I71" s="1" t="n">
+        <v>241.55</v>
       </c>
     </row>
     <row r="72">
       <c r="H72" s="1" t="n">
-        <v>722.09</v>
+        <v>241.55</v>
       </c>
       <c r="I72" s="1" t="n">
-        <v>722.09</v>
+        <v>241.55</v>
       </c>
     </row>
     <row r="73">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="H79" s="1" t="n">
-        <v>133449.16</v>
+        <v>133425.67</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
@@ -2058,15 +2058,15 @@
         </is>
       </c>
       <c r="I80" s="1" t="n">
-        <v>133449.16</v>
+        <v>133425.67</v>
       </c>
     </row>
     <row r="81">
       <c r="H81" s="1" t="n">
-        <v>133449.16</v>
+        <v>133425.67</v>
       </c>
       <c r="I81" s="1" t="n">
-        <v>133449.16</v>
+        <v>133425.67</v>
       </c>
     </row>
     <row r="82">
@@ -2217,7 +2217,7 @@
         </is>
       </c>
       <c r="H88" s="1" t="n">
-        <v>8124.91</v>
+        <v>7866.58</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
@@ -2238,15 +2238,15 @@
         </is>
       </c>
       <c r="I89" s="1" t="n">
-        <v>8124.91</v>
+        <v>7866.58</v>
       </c>
     </row>
     <row r="90">
       <c r="H90" s="1" t="n">
-        <v>8124.91</v>
+        <v>7866.58</v>
       </c>
       <c r="I90" s="1" t="n">
-        <v>8124.91</v>
+        <v>7866.58</v>
       </c>
     </row>
     <row r="91">
@@ -2281,7 +2281,7 @@
         </is>
       </c>
       <c r="H91" s="1" t="n">
-        <v>7989</v>
+        <v>7730.67</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
@@ -2306,15 +2306,15 @@
         </is>
       </c>
       <c r="I92" s="1" t="n">
-        <v>7989</v>
+        <v>7730.67</v>
       </c>
     </row>
     <row r="93">
       <c r="H93" s="1" t="n">
-        <v>7989</v>
+        <v>7730.67</v>
       </c>
       <c r="I93" s="1" t="n">
-        <v>7989</v>
+        <v>7730.67</v>
       </c>
     </row>
     <row r="94">
@@ -3357,7 +3357,7 @@
         </is>
       </c>
       <c r="H143" s="1" t="n">
-        <v>1024.64</v>
+        <v>959.62</v>
       </c>
       <c r="J143" t="inlineStr">
         <is>
@@ -3382,15 +3382,15 @@
         </is>
       </c>
       <c r="I144" s="1" t="n">
-        <v>1024.64</v>
+        <v>959.62</v>
       </c>
     </row>
     <row r="145">
       <c r="H145" s="1" t="n">
-        <v>1024.64</v>
+        <v>959.62</v>
       </c>
       <c r="I145" s="1" t="n">
-        <v>1024.64</v>
+        <v>959.62</v>
       </c>
     </row>
     <row r="146">
@@ -3484,8 +3484,8 @@
           <t>67000 Office Supplies</t>
         </is>
       </c>
-      <c r="I149" s="1" t="n">
-        <v>714</v>
+      <c r="H149" s="1" t="n">
+        <v>169.33</v>
       </c>
       <c r="J149" t="inlineStr">
         <is>
@@ -3509,16 +3509,16 @@
           <t>20000 Accounts Payable (A/P)</t>
         </is>
       </c>
-      <c r="H150" s="1" t="n">
-        <v>714</v>
+      <c r="I150" s="1" t="n">
+        <v>169.33</v>
       </c>
     </row>
     <row r="151">
       <c r="H151" s="1" t="n">
-        <v>714</v>
+        <v>169.33</v>
       </c>
       <c r="I151" s="1" t="n">
-        <v>714</v>
+        <v>169.33</v>
       </c>
     </row>
     <row r="152">
@@ -4281,8 +4281,8 @@
           <t>20000 Accounts Payable (A/P)</t>
         </is>
       </c>
-      <c r="I188" s="1" t="n">
-        <v>722.09</v>
+      <c r="H188" s="1" t="n">
+        <v>241.55</v>
       </c>
       <c r="J188" t="inlineStr">
         <is>
@@ -4302,16 +4302,16 @@
           <t>10100 Checking - First Prairie</t>
         </is>
       </c>
-      <c r="H189" s="1" t="n">
-        <v>722.09</v>
+      <c r="I189" s="1" t="n">
+        <v>241.55</v>
       </c>
     </row>
     <row r="190">
       <c r="H190" s="1" t="n">
-        <v>722.09</v>
+        <v>241.55</v>
       </c>
       <c r="I190" s="1" t="n">
-        <v>722.09</v>
+        <v>241.55</v>
       </c>
     </row>
     <row r="191">
@@ -4462,7 +4462,7 @@
         </is>
       </c>
       <c r="H197" s="1" t="n">
-        <v>133449.16</v>
+        <v>133425.67</v>
       </c>
       <c r="J197" t="inlineStr">
         <is>
@@ -4483,15 +4483,15 @@
         </is>
       </c>
       <c r="I198" s="1" t="n">
-        <v>133449.16</v>
+        <v>133425.67</v>
       </c>
     </row>
     <row r="199">
       <c r="H199" s="1" t="n">
-        <v>133449.16</v>
+        <v>133425.67</v>
       </c>
       <c r="I199" s="1" t="n">
-        <v>133449.16</v>
+        <v>133425.67</v>
       </c>
     </row>
     <row r="200">
@@ -4642,7 +4642,7 @@
         </is>
       </c>
       <c r="H206" s="1" t="n">
-        <v>8124.91</v>
+        <v>7866.58</v>
       </c>
       <c r="J206" t="inlineStr">
         <is>
@@ -4663,15 +4663,15 @@
         </is>
       </c>
       <c r="I207" s="1" t="n">
-        <v>8124.91</v>
+        <v>7866.58</v>
       </c>
     </row>
     <row r="208">
       <c r="H208" s="1" t="n">
-        <v>8124.91</v>
+        <v>7866.58</v>
       </c>
       <c r="I208" s="1" t="n">
-        <v>8124.91</v>
+        <v>7866.58</v>
       </c>
     </row>
     <row r="209">
@@ -4777,7 +4777,7 @@
         </is>
       </c>
       <c r="H213" s="1" t="n">
-        <v>7989</v>
+        <v>7730.67</v>
       </c>
       <c r="J213" t="inlineStr">
         <is>
@@ -4802,15 +4802,15 @@
         </is>
       </c>
       <c r="I214" s="1" t="n">
-        <v>7989</v>
+        <v>7730.67</v>
       </c>
     </row>
     <row r="215">
       <c r="H215" s="1" t="n">
-        <v>7989</v>
+        <v>7730.67</v>
       </c>
       <c r="I215" s="1" t="n">
-        <v>7989</v>
+        <v>7730.67</v>
       </c>
     </row>
     <row r="216">
@@ -5578,7 +5578,7 @@
         </is>
       </c>
       <c r="H252" s="1" t="n">
-        <v>1024.64</v>
+        <v>959.62</v>
       </c>
       <c r="J252" t="inlineStr">
         <is>
@@ -5603,15 +5603,15 @@
         </is>
       </c>
       <c r="I253" s="1" t="n">
-        <v>1024.64</v>
+        <v>959.62</v>
       </c>
     </row>
     <row r="254">
       <c r="H254" s="1" t="n">
-        <v>1024.64</v>
+        <v>959.62</v>
       </c>
       <c r="I254" s="1" t="n">
-        <v>1024.64</v>
+        <v>959.62</v>
       </c>
     </row>
     <row r="255">
@@ -5849,8 +5849,8 @@
           <t>67000 Office Supplies</t>
         </is>
       </c>
-      <c r="I264" s="1" t="n">
-        <v>714</v>
+      <c r="H264" s="1" t="n">
+        <v>169.33</v>
       </c>
       <c r="J264" t="inlineStr">
         <is>
@@ -5874,16 +5874,16 @@
           <t>20000 Accounts Payable (A/P)</t>
         </is>
       </c>
-      <c r="H265" s="1" t="n">
-        <v>714</v>
+      <c r="I265" s="1" t="n">
+        <v>169.33</v>
       </c>
     </row>
     <row r="266">
       <c r="H266" s="1" t="n">
-        <v>714</v>
+        <v>169.33</v>
       </c>
       <c r="I266" s="1" t="n">
-        <v>714</v>
+        <v>169.33</v>
       </c>
     </row>
     <row r="267">
@@ -6638,8 +6638,8 @@
           <t>20000 Accounts Payable (A/P)</t>
         </is>
       </c>
-      <c r="I303" s="1" t="n">
-        <v>722.09</v>
+      <c r="H303" s="1" t="n">
+        <v>241.55</v>
       </c>
       <c r="J303" t="inlineStr">
         <is>
@@ -6659,16 +6659,16 @@
           <t>10100 Checking - First Prairie</t>
         </is>
       </c>
-      <c r="H304" s="1" t="n">
-        <v>722.09</v>
+      <c r="I304" s="1" t="n">
+        <v>241.55</v>
       </c>
     </row>
     <row r="305">
       <c r="H305" s="1" t="n">
-        <v>722.09</v>
+        <v>241.55</v>
       </c>
       <c r="I305" s="1" t="n">
-        <v>722.09</v>
+        <v>241.55</v>
       </c>
     </row>
     <row r="306">
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="H312" s="1" t="n">
-        <v>133449.16</v>
+        <v>133425.67</v>
       </c>
       <c r="J312" t="inlineStr">
         <is>
@@ -6840,15 +6840,15 @@
         </is>
       </c>
       <c r="I313" s="1" t="n">
-        <v>133449.16</v>
+        <v>133425.67</v>
       </c>
     </row>
     <row r="314">
       <c r="H314" s="1" t="n">
-        <v>133449.16</v>
+        <v>133425.67</v>
       </c>
       <c r="I314" s="1" t="n">
-        <v>133449.16</v>
+        <v>133425.67</v>
       </c>
     </row>
     <row r="315">
@@ -6999,7 +6999,7 @@
         </is>
       </c>
       <c r="H321" s="1" t="n">
-        <v>8124.91</v>
+        <v>7866.58</v>
       </c>
       <c r="J321" t="inlineStr">
         <is>
@@ -7020,15 +7020,15 @@
         </is>
       </c>
       <c r="I322" s="1" t="n">
-        <v>8124.91</v>
+        <v>7866.58</v>
       </c>
     </row>
     <row r="323">
       <c r="H323" s="1" t="n">
-        <v>8124.91</v>
+        <v>7866.58</v>
       </c>
       <c r="I323" s="1" t="n">
-        <v>8124.91</v>
+        <v>7866.58</v>
       </c>
     </row>
     <row r="324">
@@ -7134,7 +7134,7 @@
         </is>
       </c>
       <c r="H328" s="1" t="n">
-        <v>7989</v>
+        <v>7730.67</v>
       </c>
       <c r="J328" t="inlineStr">
         <is>
@@ -7159,15 +7159,15 @@
         </is>
       </c>
       <c r="I329" s="1" t="n">
-        <v>7989</v>
+        <v>7730.67</v>
       </c>
     </row>
     <row r="330">
       <c r="H330" s="1" t="n">
-        <v>7989</v>
+        <v>7730.67</v>
       </c>
       <c r="I330" s="1" t="n">
-        <v>7989</v>
+        <v>7730.67</v>
       </c>
     </row>
     <row r="331">
@@ -8000,7 +8000,7 @@
         </is>
       </c>
       <c r="H369" s="1" t="n">
-        <v>1024.64</v>
+        <v>959.62</v>
       </c>
       <c r="J369" t="inlineStr">
         <is>
@@ -8025,15 +8025,15 @@
         </is>
       </c>
       <c r="I370" s="1" t="n">
-        <v>1024.64</v>
+        <v>959.62</v>
       </c>
     </row>
     <row r="371">
       <c r="H371" s="1" t="n">
-        <v>1024.64</v>
+        <v>959.62</v>
       </c>
       <c r="I371" s="1" t="n">
-        <v>1024.64</v>
+        <v>959.62</v>
       </c>
     </row>
     <row r="372">
@@ -8402,8 +8402,8 @@
           <t>67000 Office Supplies</t>
         </is>
       </c>
-      <c r="I388" s="1" t="n">
-        <v>714</v>
+      <c r="H388" s="1" t="n">
+        <v>169.33</v>
       </c>
       <c r="J388" t="inlineStr">
         <is>
@@ -8427,16 +8427,16 @@
           <t>20000 Accounts Payable (A/P)</t>
         </is>
       </c>
-      <c r="H389" s="1" t="n">
-        <v>714</v>
+      <c r="I389" s="1" t="n">
+        <v>169.33</v>
       </c>
     </row>
     <row r="390">
       <c r="H390" s="1" t="n">
-        <v>714</v>
+        <v>169.33</v>
       </c>
       <c r="I390" s="1" t="n">
-        <v>714</v>
+        <v>169.33</v>
       </c>
     </row>
     <row r="391">
@@ -9016,7 +9016,7 @@
         </is>
       </c>
       <c r="H418" s="1" t="n">
-        <v>7989</v>
+        <v>7730.67</v>
       </c>
       <c r="J418" t="inlineStr">
         <is>
@@ -9041,15 +9041,15 @@
         </is>
       </c>
       <c r="I419" s="1" t="n">
-        <v>7989</v>
+        <v>7730.67</v>
       </c>
     </row>
     <row r="420">
       <c r="H420" s="1" t="n">
-        <v>7989</v>
+        <v>7730.67</v>
       </c>
       <c r="I420" s="1" t="n">
-        <v>7989</v>
+        <v>7730.67</v>
       </c>
     </row>
     <row r="421">
@@ -9199,8 +9199,8 @@
           <t>20000 Accounts Payable (A/P)</t>
         </is>
       </c>
-      <c r="I427" s="1" t="n">
-        <v>722.09</v>
+      <c r="H427" s="1" t="n">
+        <v>241.55</v>
       </c>
       <c r="J427" t="inlineStr">
         <is>
@@ -9220,16 +9220,16 @@
           <t>10100 Checking - First Prairie</t>
         </is>
       </c>
-      <c r="H428" s="1" t="n">
-        <v>722.09</v>
+      <c r="I428" s="1" t="n">
+        <v>241.55</v>
       </c>
     </row>
     <row r="429">
       <c r="H429" s="1" t="n">
-        <v>722.09</v>
+        <v>241.55</v>
       </c>
       <c r="I429" s="1" t="n">
-        <v>722.09</v>
+        <v>241.55</v>
       </c>
     </row>
     <row r="430">
@@ -9380,7 +9380,7 @@
         </is>
       </c>
       <c r="H436" s="1" t="n">
-        <v>133449.16</v>
+        <v>133425.67</v>
       </c>
       <c r="J436" t="inlineStr">
         <is>
@@ -9401,15 +9401,15 @@
         </is>
       </c>
       <c r="I437" s="1" t="n">
-        <v>133449.16</v>
+        <v>133425.67</v>
       </c>
     </row>
     <row r="438">
       <c r="H438" s="1" t="n">
-        <v>133449.16</v>
+        <v>133425.67</v>
       </c>
       <c r="I438" s="1" t="n">
-        <v>133449.16</v>
+        <v>133425.67</v>
       </c>
     </row>
     <row r="439">
@@ -9560,7 +9560,7 @@
         </is>
       </c>
       <c r="H445" s="1" t="n">
-        <v>8124.91</v>
+        <v>7866.58</v>
       </c>
       <c r="J445" t="inlineStr">
         <is>
@@ -9581,15 +9581,15 @@
         </is>
       </c>
       <c r="I446" s="1" t="n">
-        <v>8124.91</v>
+        <v>7866.58</v>
       </c>
     </row>
     <row r="447">
       <c r="H447" s="1" t="n">
-        <v>8124.91</v>
+        <v>7866.58</v>
       </c>
       <c r="I447" s="1" t="n">
-        <v>8124.91</v>
+        <v>7866.58</v>
       </c>
     </row>
     <row r="448">
@@ -10289,7 +10289,7 @@
         </is>
       </c>
       <c r="H481" s="1" t="n">
-        <v>4950</v>
+        <v>2450</v>
       </c>
       <c r="J481" t="inlineStr">
         <is>
@@ -10314,15 +10314,15 @@
         </is>
       </c>
       <c r="I482" s="1" t="n">
-        <v>4950</v>
+        <v>2450</v>
       </c>
     </row>
     <row r="483">
       <c r="H483" s="1" t="n">
-        <v>4950</v>
+        <v>2450</v>
       </c>
       <c r="I483" s="1" t="n">
-        <v>4950</v>
+        <v>2450</v>
       </c>
     </row>
     <row r="484">
@@ -10425,7 +10425,7 @@
         </is>
       </c>
       <c r="H487" s="1" t="n">
-        <v>4975</v>
+        <v>2475</v>
       </c>
       <c r="J487" t="inlineStr">
         <is>
@@ -10450,15 +10450,15 @@
         </is>
       </c>
       <c r="I488" s="1" t="n">
-        <v>4975</v>
+        <v>2475</v>
       </c>
     </row>
     <row r="489">
       <c r="H489" s="1" t="n">
-        <v>4975</v>
+        <v>2475</v>
       </c>
       <c r="I489" s="1" t="n">
-        <v>4975</v>
+        <v>2475</v>
       </c>
     </row>
     <row r="490">
@@ -10564,7 +10564,7 @@
         </is>
       </c>
       <c r="H494" s="1" t="n">
-        <v>1024.64</v>
+        <v>959.62</v>
       </c>
       <c r="J494" t="inlineStr">
         <is>
@@ -10589,15 +10589,15 @@
         </is>
       </c>
       <c r="I495" s="1" t="n">
-        <v>1024.64</v>
+        <v>959.62</v>
       </c>
     </row>
     <row r="496">
       <c r="H496" s="1" t="n">
-        <v>1024.64</v>
+        <v>959.62</v>
       </c>
       <c r="I496" s="1" t="n">
-        <v>1024.64</v>
+        <v>959.62</v>
       </c>
     </row>
     <row r="497">
@@ -10632,7 +10632,7 @@
         </is>
       </c>
       <c r="H497" s="1" t="n">
-        <v>4900</v>
+        <v>2400</v>
       </c>
       <c r="J497" t="inlineStr">
         <is>
@@ -10657,15 +10657,15 @@
         </is>
       </c>
       <c r="I498" s="1" t="n">
-        <v>4900</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="499">
       <c r="H499" s="1" t="n">
-        <v>4900</v>
+        <v>2400</v>
       </c>
       <c r="I499" s="1" t="n">
-        <v>4900</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="500">
@@ -10963,8 +10963,8 @@
           <t>67000 Office Supplies</t>
         </is>
       </c>
-      <c r="I512" s="1" t="n">
-        <v>714</v>
+      <c r="H512" s="1" t="n">
+        <v>169.33</v>
       </c>
       <c r="J512" t="inlineStr">
         <is>
@@ -10988,16 +10988,16 @@
           <t>20000 Accounts Payable (A/P)</t>
         </is>
       </c>
-      <c r="H513" s="1" t="n">
-        <v>714</v>
+      <c r="I513" s="1" t="n">
+        <v>169.33</v>
       </c>
     </row>
     <row r="514">
       <c r="H514" s="1" t="n">
-        <v>714</v>
+        <v>169.33</v>
       </c>
       <c r="I514" s="1" t="n">
-        <v>714</v>
+        <v>169.33</v>
       </c>
     </row>
     <row r="515">
@@ -11291,7 +11291,7 @@
         </is>
       </c>
       <c r="H528" s="1" t="n">
-        <v>4950</v>
+        <v>2450</v>
       </c>
       <c r="J528" t="inlineStr">
         <is>
@@ -11312,15 +11312,15 @@
         </is>
       </c>
       <c r="I529" s="1" t="n">
-        <v>4950</v>
+        <v>2450</v>
       </c>
     </row>
     <row r="530">
       <c r="H530" s="1" t="n">
-        <v>4950</v>
+        <v>2450</v>
       </c>
       <c r="I530" s="1" t="n">
-        <v>4950</v>
+        <v>2450</v>
       </c>
     </row>
     <row r="531">
@@ -11351,7 +11351,7 @@
         </is>
       </c>
       <c r="H531" s="1" t="n">
-        <v>4975</v>
+        <v>2475</v>
       </c>
       <c r="J531" t="inlineStr">
         <is>
@@ -11372,15 +11372,15 @@
         </is>
       </c>
       <c r="I532" s="1" t="n">
-        <v>4975</v>
+        <v>2475</v>
       </c>
     </row>
     <row r="533">
       <c r="H533" s="1" t="n">
-        <v>4975</v>
+        <v>2475</v>
       </c>
       <c r="I533" s="1" t="n">
-        <v>4975</v>
+        <v>2475</v>
       </c>
     </row>
     <row r="534">
@@ -11411,7 +11411,7 @@
         </is>
       </c>
       <c r="H534" s="1" t="n">
-        <v>4900</v>
+        <v>2400</v>
       </c>
       <c r="J534" t="inlineStr">
         <is>
@@ -11432,15 +11432,15 @@
         </is>
       </c>
       <c r="I535" s="1" t="n">
-        <v>4900</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="536">
       <c r="H536" s="1" t="n">
-        <v>4900</v>
+        <v>2400</v>
       </c>
       <c r="I536" s="1" t="n">
-        <v>4900</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="537">
@@ -11868,8 +11868,8 @@
           <t>20000 Accounts Payable (A/P)</t>
         </is>
       </c>
-      <c r="I557" s="1" t="n">
-        <v>722.09</v>
+      <c r="H557" s="1" t="n">
+        <v>241.55</v>
       </c>
       <c r="J557" t="inlineStr">
         <is>
@@ -11889,16 +11889,16 @@
           <t>10100 Checking - First Prairie</t>
         </is>
       </c>
-      <c r="H558" s="1" t="n">
-        <v>722.09</v>
+      <c r="I558" s="1" t="n">
+        <v>241.55</v>
       </c>
     </row>
     <row r="559">
       <c r="H559" s="1" t="n">
-        <v>722.09</v>
+        <v>241.55</v>
       </c>
       <c r="I559" s="1" t="n">
-        <v>722.09</v>
+        <v>241.55</v>
       </c>
     </row>
     <row r="560">
@@ -12049,7 +12049,7 @@
         </is>
       </c>
       <c r="H566" s="1" t="n">
-        <v>133449.16</v>
+        <v>133425.67</v>
       </c>
       <c r="J566" t="inlineStr">
         <is>
@@ -12070,15 +12070,15 @@
         </is>
       </c>
       <c r="I567" s="1" t="n">
-        <v>133449.16</v>
+        <v>133425.67</v>
       </c>
     </row>
     <row r="568">
       <c r="H568" s="1" t="n">
-        <v>133449.16</v>
+        <v>133425.67</v>
       </c>
       <c r="I568" s="1" t="n">
-        <v>133449.16</v>
+        <v>133425.67</v>
       </c>
     </row>
     <row r="569">
@@ -12229,7 +12229,7 @@
         </is>
       </c>
       <c r="H575" s="1" t="n">
-        <v>8124.91</v>
+        <v>7866.58</v>
       </c>
       <c r="J575" t="inlineStr">
         <is>
@@ -12250,15 +12250,15 @@
         </is>
       </c>
       <c r="I576" s="1" t="n">
-        <v>8124.91</v>
+        <v>7866.58</v>
       </c>
     </row>
     <row r="577">
       <c r="H577" s="1" t="n">
-        <v>8124.91</v>
+        <v>7866.58</v>
       </c>
       <c r="I577" s="1" t="n">
-        <v>8124.91</v>
+        <v>7866.58</v>
       </c>
     </row>
     <row r="578">
@@ -12364,7 +12364,7 @@
         </is>
       </c>
       <c r="H582" s="1" t="n">
-        <v>7989</v>
+        <v>7730.67</v>
       </c>
       <c r="J582" t="inlineStr">
         <is>
@@ -12389,15 +12389,15 @@
         </is>
       </c>
       <c r="I583" s="1" t="n">
-        <v>7989</v>
+        <v>7730.67</v>
       </c>
     </row>
     <row r="584">
       <c r="H584" s="1" t="n">
-        <v>7989</v>
+        <v>7730.67</v>
       </c>
       <c r="I584" s="1" t="n">
-        <v>7989</v>
+        <v>7730.67</v>
       </c>
     </row>
     <row r="585">
@@ -13369,7 +13369,7 @@
         </is>
       </c>
       <c r="H630" s="1" t="n">
-        <v>1024.64</v>
+        <v>959.62</v>
       </c>
       <c r="J630" t="inlineStr">
         <is>
@@ -13394,15 +13394,15 @@
         </is>
       </c>
       <c r="I631" s="1" t="n">
-        <v>1024.64</v>
+        <v>959.62</v>
       </c>
     </row>
     <row r="632">
       <c r="H632" s="1" t="n">
-        <v>1024.64</v>
+        <v>959.62</v>
       </c>
       <c r="I632" s="1" t="n">
-        <v>1024.64</v>
+        <v>959.62</v>
       </c>
     </row>
     <row r="633">
@@ -13436,8 +13436,8 @@
           <t>67000 Office Supplies</t>
         </is>
       </c>
-      <c r="I633" s="1" t="n">
-        <v>714</v>
+      <c r="H633" s="1" t="n">
+        <v>169.33</v>
       </c>
       <c r="J633" t="inlineStr">
         <is>
@@ -13461,16 +13461,16 @@
           <t>20000 Accounts Payable (A/P)</t>
         </is>
       </c>
-      <c r="H634" s="1" t="n">
-        <v>714</v>
+      <c r="I634" s="1" t="n">
+        <v>169.33</v>
       </c>
     </row>
     <row r="635">
       <c r="H635" s="1" t="n">
-        <v>714</v>
+        <v>169.33</v>
       </c>
       <c r="I635" s="1" t="n">
-        <v>714</v>
+        <v>169.33</v>
       </c>
     </row>
     <row r="636">
@@ -14225,8 +14225,8 @@
           <t>20000 Accounts Payable (A/P)</t>
         </is>
       </c>
-      <c r="I672" s="1" t="n">
-        <v>722.09</v>
+      <c r="H672" s="1" t="n">
+        <v>241.55</v>
       </c>
       <c r="J672" t="inlineStr">
         <is>
@@ -14246,16 +14246,16 @@
           <t>10100 Checking - First Prairie</t>
         </is>
       </c>
-      <c r="H673" s="1" t="n">
-        <v>722.09</v>
+      <c r="I673" s="1" t="n">
+        <v>241.55</v>
       </c>
     </row>
     <row r="674">
       <c r="H674" s="1" t="n">
-        <v>722.09</v>
+        <v>241.55</v>
       </c>
       <c r="I674" s="1" t="n">
-        <v>722.09</v>
+        <v>241.55</v>
       </c>
     </row>
     <row r="675">
@@ -14406,7 +14406,7 @@
         </is>
       </c>
       <c r="H681" s="1" t="n">
-        <v>133449.16</v>
+        <v>133425.67</v>
       </c>
       <c r="J681" t="inlineStr">
         <is>
@@ -14427,15 +14427,15 @@
         </is>
       </c>
       <c r="I682" s="1" t="n">
-        <v>133449.16</v>
+        <v>133425.67</v>
       </c>
     </row>
     <row r="683">
       <c r="H683" s="1" t="n">
-        <v>133449.16</v>
+        <v>133425.67</v>
       </c>
       <c r="I683" s="1" t="n">
-        <v>133449.16</v>
+        <v>133425.67</v>
       </c>
     </row>
     <row r="684">
@@ -14586,7 +14586,7 @@
         </is>
       </c>
       <c r="H690" s="1" t="n">
-        <v>8124.91</v>
+        <v>7866.58</v>
       </c>
       <c r="J690" t="inlineStr">
         <is>
@@ -14607,15 +14607,15 @@
         </is>
       </c>
       <c r="I691" s="1" t="n">
-        <v>8124.91</v>
+        <v>7866.58</v>
       </c>
     </row>
     <row r="692">
       <c r="H692" s="1" t="n">
-        <v>8124.91</v>
+        <v>7866.58</v>
       </c>
       <c r="I692" s="1" t="n">
-        <v>8124.91</v>
+        <v>7866.58</v>
       </c>
     </row>
     <row r="693">
@@ -14721,7 +14721,7 @@
         </is>
       </c>
       <c r="H697" s="1" t="n">
-        <v>7989</v>
+        <v>7730.67</v>
       </c>
       <c r="J697" t="inlineStr">
         <is>
@@ -14746,15 +14746,15 @@
         </is>
       </c>
       <c r="I698" s="1" t="n">
-        <v>7989</v>
+        <v>7730.67</v>
       </c>
     </row>
     <row r="699">
       <c r="H699" s="1" t="n">
-        <v>7989</v>
+        <v>7730.67</v>
       </c>
       <c r="I699" s="1" t="n">
-        <v>7989</v>
+        <v>7730.67</v>
       </c>
     </row>
     <row r="700">
@@ -15519,7 +15519,7 @@
         </is>
       </c>
       <c r="H735" s="1" t="n">
-        <v>1024.64</v>
+        <v>959.62</v>
       </c>
       <c r="J735" t="inlineStr">
         <is>
@@ -15544,15 +15544,15 @@
         </is>
       </c>
       <c r="I736" s="1" t="n">
-        <v>1024.64</v>
+        <v>959.62</v>
       </c>
     </row>
     <row r="737">
       <c r="H737" s="1" t="n">
-        <v>1024.64</v>
+        <v>959.62</v>
       </c>
       <c r="I737" s="1" t="n">
-        <v>1024.64</v>
+        <v>959.62</v>
       </c>
     </row>
     <row r="738">
@@ -15921,8 +15921,8 @@
           <t>67000 Office Supplies</t>
         </is>
       </c>
-      <c r="I754" s="1" t="n">
-        <v>714</v>
+      <c r="H754" s="1" t="n">
+        <v>169.33</v>
       </c>
       <c r="J754" t="inlineStr">
         <is>
@@ -15946,16 +15946,16 @@
           <t>20000 Accounts Payable (A/P)</t>
         </is>
       </c>
-      <c r="H755" s="1" t="n">
-        <v>714</v>
+      <c r="I755" s="1" t="n">
+        <v>169.33</v>
       </c>
     </row>
     <row r="756">
       <c r="H756" s="1" t="n">
-        <v>714</v>
+        <v>169.33</v>
       </c>
       <c r="I756" s="1" t="n">
-        <v>714</v>
+        <v>169.33</v>
       </c>
     </row>
     <row r="757">
@@ -16650,8 +16650,8 @@
           <t>20000 Accounts Payable (A/P)</t>
         </is>
       </c>
-      <c r="I790" s="1" t="n">
-        <v>722.09</v>
+      <c r="H790" s="1" t="n">
+        <v>241.55</v>
       </c>
       <c r="J790" t="inlineStr">
         <is>
@@ -16671,16 +16671,16 @@
           <t>10100 Checking - First Prairie</t>
         </is>
       </c>
-      <c r="H791" s="1" t="n">
-        <v>722.09</v>
+      <c r="I791" s="1" t="n">
+        <v>241.55</v>
       </c>
     </row>
     <row r="792">
       <c r="H792" s="1" t="n">
-        <v>722.09</v>
+        <v>241.55</v>
       </c>
       <c r="I792" s="1" t="n">
-        <v>722.09</v>
+        <v>241.55</v>
       </c>
     </row>
     <row r="793">
@@ -16831,7 +16831,7 @@
         </is>
       </c>
       <c r="H799" s="1" t="n">
-        <v>133449.16</v>
+        <v>133425.67</v>
       </c>
       <c r="J799" t="inlineStr">
         <is>
@@ -16852,15 +16852,15 @@
         </is>
       </c>
       <c r="I800" s="1" t="n">
-        <v>133449.16</v>
+        <v>133425.67</v>
       </c>
     </row>
     <row r="801">
       <c r="H801" s="1" t="n">
-        <v>133449.16</v>
+        <v>133425.67</v>
       </c>
       <c r="I801" s="1" t="n">
-        <v>133449.16</v>
+        <v>133425.67</v>
       </c>
     </row>
     <row r="802">
@@ -17011,7 +17011,7 @@
         </is>
       </c>
       <c r="H808" s="1" t="n">
-        <v>8124.91</v>
+        <v>7866.58</v>
       </c>
       <c r="J808" t="inlineStr">
         <is>
@@ -17032,15 +17032,15 @@
         </is>
       </c>
       <c r="I809" s="1" t="n">
-        <v>8124.91</v>
+        <v>7866.58</v>
       </c>
     </row>
     <row r="810">
       <c r="H810" s="1" t="n">
-        <v>8124.91</v>
+        <v>7866.58</v>
       </c>
       <c r="I810" s="1" t="n">
-        <v>8124.91</v>
+        <v>7866.58</v>
       </c>
     </row>
     <row r="811">
@@ -17146,7 +17146,7 @@
         </is>
       </c>
       <c r="H815" s="1" t="n">
-        <v>7989</v>
+        <v>7730.67</v>
       </c>
       <c r="J815" t="inlineStr">
         <is>
@@ -17171,15 +17171,15 @@
         </is>
       </c>
       <c r="I816" s="1" t="n">
-        <v>7989</v>
+        <v>7730.67</v>
       </c>
     </row>
     <row r="817">
       <c r="H817" s="1" t="n">
-        <v>7989</v>
+        <v>7730.67</v>
       </c>
       <c r="I817" s="1" t="n">
-        <v>7989</v>
+        <v>7730.67</v>
       </c>
     </row>
     <row r="818">
@@ -18011,7 +18011,7 @@
         </is>
       </c>
       <c r="H857" s="1" t="n">
-        <v>1024.64</v>
+        <v>959.62</v>
       </c>
       <c r="J857" t="inlineStr">
         <is>
@@ -18036,15 +18036,15 @@
         </is>
       </c>
       <c r="I858" s="1" t="n">
-        <v>1024.64</v>
+        <v>959.62</v>
       </c>
     </row>
     <row r="859">
       <c r="H859" s="1" t="n">
-        <v>1024.64</v>
+        <v>959.62</v>
       </c>
       <c r="I859" s="1" t="n">
-        <v>1024.64</v>
+        <v>959.62</v>
       </c>
     </row>
     <row r="860">
@@ -18342,8 +18342,8 @@
           <t>67000 Office Supplies</t>
         </is>
       </c>
-      <c r="I872" s="1" t="n">
-        <v>714</v>
+      <c r="H872" s="1" t="n">
+        <v>169.33</v>
       </c>
       <c r="J872" t="inlineStr">
         <is>
@@ -18367,16 +18367,16 @@
           <t>20000 Accounts Payable (A/P)</t>
         </is>
       </c>
-      <c r="H873" s="1" t="n">
-        <v>714</v>
+      <c r="I873" s="1" t="n">
+        <v>169.33</v>
       </c>
     </row>
     <row r="874">
       <c r="H874" s="1" t="n">
-        <v>714</v>
+        <v>169.33</v>
       </c>
       <c r="I874" s="1" t="n">
-        <v>714</v>
+        <v>169.33</v>
       </c>
     </row>
     <row r="875">
@@ -19127,8 +19127,8 @@
           <t>20000 Accounts Payable (A/P)</t>
         </is>
       </c>
-      <c r="I911" s="1" t="n">
-        <v>722.09</v>
+      <c r="H911" s="1" t="n">
+        <v>241.55</v>
       </c>
       <c r="J911" t="inlineStr">
         <is>
@@ -19148,16 +19148,16 @@
           <t>10100 Checking - First Prairie</t>
         </is>
       </c>
-      <c r="H912" s="1" t="n">
-        <v>722.09</v>
+      <c r="I912" s="1" t="n">
+        <v>241.55</v>
       </c>
     </row>
     <row r="913">
       <c r="H913" s="1" t="n">
-        <v>722.09</v>
+        <v>241.55</v>
       </c>
       <c r="I913" s="1" t="n">
-        <v>722.09</v>
+        <v>241.55</v>
       </c>
     </row>
     <row r="914">
@@ -19308,7 +19308,7 @@
         </is>
       </c>
       <c r="H920" s="1" t="n">
-        <v>133449.16</v>
+        <v>133425.67</v>
       </c>
       <c r="J920" t="inlineStr">
         <is>
@@ -19329,15 +19329,15 @@
         </is>
       </c>
       <c r="I921" s="1" t="n">
-        <v>133449.16</v>
+        <v>133425.67</v>
       </c>
     </row>
     <row r="922">
       <c r="H922" s="1" t="n">
-        <v>133449.16</v>
+        <v>133425.67</v>
       </c>
       <c r="I922" s="1" t="n">
-        <v>133449.16</v>
+        <v>133425.67</v>
       </c>
     </row>
     <row r="923">
@@ -19488,7 +19488,7 @@
         </is>
       </c>
       <c r="H929" s="1" t="n">
-        <v>8124.91</v>
+        <v>7866.58</v>
       </c>
       <c r="J929" t="inlineStr">
         <is>
@@ -19509,15 +19509,15 @@
         </is>
       </c>
       <c r="I930" s="1" t="n">
-        <v>8124.91</v>
+        <v>7866.58</v>
       </c>
     </row>
     <row r="931">
       <c r="H931" s="1" t="n">
-        <v>8124.91</v>
+        <v>7866.58</v>
       </c>
       <c r="I931" s="1" t="n">
-        <v>8124.91</v>
+        <v>7866.58</v>
       </c>
     </row>
     <row r="932">
@@ -19623,7 +19623,7 @@
         </is>
       </c>
       <c r="H936" s="1" t="n">
-        <v>7989</v>
+        <v>7730.67</v>
       </c>
       <c r="J936" t="inlineStr">
         <is>
@@ -19648,15 +19648,15 @@
         </is>
       </c>
       <c r="I937" s="1" t="n">
-        <v>7989</v>
+        <v>7730.67</v>
       </c>
     </row>
     <row r="938">
       <c r="H938" s="1" t="n">
-        <v>7989</v>
+        <v>7730.67</v>
       </c>
       <c r="I938" s="1" t="n">
-        <v>7989</v>
+        <v>7730.67</v>
       </c>
     </row>
     <row r="939">
@@ -20424,7 +20424,7 @@
         </is>
       </c>
       <c r="H975" s="1" t="n">
-        <v>1024.64</v>
+        <v>959.62</v>
       </c>
       <c r="J975" t="inlineStr">
         <is>
@@ -20449,15 +20449,15 @@
         </is>
       </c>
       <c r="I976" s="1" t="n">
-        <v>1024.64</v>
+        <v>959.62</v>
       </c>
     </row>
     <row r="977">
       <c r="H977" s="1" t="n">
-        <v>1024.64</v>
+        <v>959.62</v>
       </c>
       <c r="I977" s="1" t="n">
-        <v>1024.64</v>
+        <v>959.62</v>
       </c>
     </row>
     <row r="978">
@@ -20755,8 +20755,8 @@
           <t>67000 Office Supplies</t>
         </is>
       </c>
-      <c r="I990" s="1" t="n">
-        <v>714</v>
+      <c r="H990" s="1" t="n">
+        <v>169.33</v>
       </c>
       <c r="J990" t="inlineStr">
         <is>
@@ -20780,16 +20780,16 @@
           <t>20000 Accounts Payable (A/P)</t>
         </is>
       </c>
-      <c r="H991" s="1" t="n">
-        <v>714</v>
+      <c r="I991" s="1" t="n">
+        <v>169.33</v>
       </c>
     </row>
     <row r="992">
       <c r="H992" s="1" t="n">
-        <v>714</v>
+        <v>169.33</v>
       </c>
       <c r="I992" s="1" t="n">
-        <v>714</v>
+        <v>169.33</v>
       </c>
     </row>
     <row r="993">
@@ -21608,8 +21608,8 @@
           <t>20000 Accounts Payable (A/P)</t>
         </is>
       </c>
-      <c r="I1032" s="1" t="n">
-        <v>722.09</v>
+      <c r="H1032" s="1" t="n">
+        <v>241.55</v>
       </c>
       <c r="J1032" t="inlineStr">
         <is>
@@ -21629,16 +21629,16 @@
           <t>10100 Checking - First Prairie</t>
         </is>
       </c>
-      <c r="H1033" s="1" t="n">
-        <v>722.09</v>
+      <c r="I1033" s="1" t="n">
+        <v>241.55</v>
       </c>
     </row>
     <row r="1034">
       <c r="H1034" s="1" t="n">
-        <v>722.09</v>
+        <v>241.55</v>
       </c>
       <c r="I1034" s="1" t="n">
-        <v>722.09</v>
+        <v>241.55</v>
       </c>
     </row>
     <row r="1035">
@@ -21789,7 +21789,7 @@
         </is>
       </c>
       <c r="H1041" s="1" t="n">
-        <v>133449.16</v>
+        <v>133425.67</v>
       </c>
       <c r="J1041" t="inlineStr">
         <is>
@@ -21810,15 +21810,15 @@
         </is>
       </c>
       <c r="I1042" s="1" t="n">
-        <v>133449.16</v>
+        <v>133425.67</v>
       </c>
     </row>
     <row r="1043">
       <c r="H1043" s="1" t="n">
-        <v>133449.16</v>
+        <v>133425.67</v>
       </c>
       <c r="I1043" s="1" t="n">
-        <v>133449.16</v>
+        <v>133425.67</v>
       </c>
     </row>
     <row r="1044">
@@ -21969,7 +21969,7 @@
         </is>
       </c>
       <c r="H1050" s="1" t="n">
-        <v>8124.91</v>
+        <v>7866.58</v>
       </c>
       <c r="J1050" t="inlineStr">
         <is>
@@ -21990,15 +21990,15 @@
         </is>
       </c>
       <c r="I1051" s="1" t="n">
-        <v>8124.91</v>
+        <v>7866.58</v>
       </c>
     </row>
     <row r="1052">
       <c r="H1052" s="1" t="n">
-        <v>8124.91</v>
+        <v>7866.58</v>
       </c>
       <c r="I1052" s="1" t="n">
-        <v>8124.91</v>
+        <v>7866.58</v>
       </c>
     </row>
     <row r="1053">
@@ -22104,7 +22104,7 @@
         </is>
       </c>
       <c r="H1057" s="1" t="n">
-        <v>7989</v>
+        <v>7730.67</v>
       </c>
       <c r="J1057" t="inlineStr">
         <is>
@@ -22129,15 +22129,15 @@
         </is>
       </c>
       <c r="I1058" s="1" t="n">
-        <v>7989</v>
+        <v>7730.67</v>
       </c>
     </row>
     <row r="1059">
       <c r="H1059" s="1" t="n">
-        <v>7989</v>
+        <v>7730.67</v>
       </c>
       <c r="I1059" s="1" t="n">
-        <v>7989</v>
+        <v>7730.67</v>
       </c>
     </row>
     <row r="1060">
@@ -22962,7 +22962,7 @@
         </is>
       </c>
       <c r="H1098" s="1" t="n">
-        <v>1024.64</v>
+        <v>959.62</v>
       </c>
       <c r="J1098" t="inlineStr">
         <is>
@@ -22987,15 +22987,15 @@
         </is>
       </c>
       <c r="I1099" s="1" t="n">
-        <v>1024.64</v>
+        <v>959.62</v>
       </c>
     </row>
     <row r="1100">
       <c r="H1100" s="1" t="n">
-        <v>1024.64</v>
+        <v>959.62</v>
       </c>
       <c r="I1100" s="1" t="n">
-        <v>1024.64</v>
+        <v>959.62</v>
       </c>
     </row>
     <row r="1101">
@@ -23364,8 +23364,8 @@
           <t>67000 Office Supplies</t>
         </is>
       </c>
-      <c r="I1117" s="1" t="n">
-        <v>714</v>
+      <c r="H1117" s="1" t="n">
+        <v>169.33</v>
       </c>
       <c r="J1117" t="inlineStr">
         <is>
@@ -23389,16 +23389,16 @@
           <t>20000 Accounts Payable (A/P)</t>
         </is>
       </c>
-      <c r="H1118" s="1" t="n">
-        <v>714</v>
+      <c r="I1118" s="1" t="n">
+        <v>169.33</v>
       </c>
     </row>
     <row r="1119">
       <c r="H1119" s="1" t="n">
-        <v>714</v>
+        <v>169.33</v>
       </c>
       <c r="I1119" s="1" t="n">
-        <v>714</v>
+        <v>169.33</v>
       </c>
     </row>
     <row r="1120">
@@ -23974,7 +23974,7 @@
         </is>
       </c>
       <c r="H1147" s="1" t="n">
-        <v>7989</v>
+        <v>7730.67</v>
       </c>
       <c r="J1147" t="inlineStr">
         <is>
@@ -23999,15 +23999,15 @@
         </is>
       </c>
       <c r="I1148" s="1" t="n">
-        <v>7989</v>
+        <v>7730.67</v>
       </c>
     </row>
     <row r="1149">
       <c r="H1149" s="1" t="n">
-        <v>7989</v>
+        <v>7730.67</v>
       </c>
       <c r="I1149" s="1" t="n">
-        <v>7989</v>
+        <v>7730.67</v>
       </c>
     </row>
     <row r="1150">
@@ -24157,8 +24157,8 @@
           <t>20000 Accounts Payable (A/P)</t>
         </is>
       </c>
-      <c r="I1156" s="1" t="n">
-        <v>722.09</v>
+      <c r="H1156" s="1" t="n">
+        <v>241.55</v>
       </c>
       <c r="J1156" t="inlineStr">
         <is>
@@ -24178,16 +24178,16 @@
           <t>10100 Checking - First Prairie</t>
         </is>
       </c>
-      <c r="H1157" s="1" t="n">
-        <v>722.09</v>
+      <c r="I1157" s="1" t="n">
+        <v>241.55</v>
       </c>
     </row>
     <row r="1158">
       <c r="H1158" s="1" t="n">
-        <v>722.09</v>
+        <v>241.55</v>
       </c>
       <c r="I1158" s="1" t="n">
-        <v>722.09</v>
+        <v>241.55</v>
       </c>
     </row>
     <row r="1159">
@@ -24338,7 +24338,7 @@
         </is>
       </c>
       <c r="H1165" s="1" t="n">
-        <v>133449.16</v>
+        <v>133425.67</v>
       </c>
       <c r="J1165" t="inlineStr">
         <is>
@@ -24359,15 +24359,15 @@
         </is>
       </c>
       <c r="I1166" s="1" t="n">
-        <v>133449.16</v>
+        <v>133425.67</v>
       </c>
     </row>
     <row r="1167">
       <c r="H1167" s="1" t="n">
-        <v>133449.16</v>
+        <v>133425.67</v>
       </c>
       <c r="I1167" s="1" t="n">
-        <v>133449.16</v>
+        <v>133425.67</v>
       </c>
     </row>
     <row r="1168">
@@ -24518,7 +24518,7 @@
         </is>
       </c>
       <c r="H1174" s="1" t="n">
-        <v>8124.91</v>
+        <v>7866.58</v>
       </c>
       <c r="J1174" t="inlineStr">
         <is>
@@ -24539,15 +24539,15 @@
         </is>
       </c>
       <c r="I1175" s="1" t="n">
-        <v>8124.91</v>
+        <v>7866.58</v>
       </c>
     </row>
     <row r="1176">
       <c r="H1176" s="1" t="n">
-        <v>8124.91</v>
+        <v>7866.58</v>
       </c>
       <c r="I1176" s="1" t="n">
-        <v>8124.91</v>
+        <v>7866.58</v>
       </c>
     </row>
     <row r="1177">
@@ -25590,7 +25590,7 @@
         </is>
       </c>
       <c r="H1226" s="1" t="n">
-        <v>179.31</v>
+        <v>959.5700000000001</v>
       </c>
       <c r="J1226" t="inlineStr">
         <is>
@@ -25615,15 +25615,15 @@
         </is>
       </c>
       <c r="I1227" s="1" t="n">
-        <v>179.31</v>
+        <v>959.5700000000001</v>
       </c>
     </row>
     <row r="1228">
       <c r="H1228" s="1" t="n">
-        <v>179.31</v>
+        <v>959.5700000000001</v>
       </c>
       <c r="I1228" s="1" t="n">
-        <v>179.31</v>
+        <v>959.5700000000001</v>
       </c>
     </row>
     <row r="1229">
@@ -25717,8 +25717,8 @@
           <t>67000 Office Supplies</t>
         </is>
       </c>
-      <c r="I1232" s="1" t="n">
-        <v>714</v>
+      <c r="H1232" s="1" t="n">
+        <v>169.33</v>
       </c>
       <c r="J1232" t="inlineStr">
         <is>
@@ -25742,16 +25742,16 @@
           <t>20000 Accounts Payable (A/P)</t>
         </is>
       </c>
-      <c r="H1233" s="1" t="n">
-        <v>714</v>
+      <c r="I1233" s="1" t="n">
+        <v>169.33</v>
       </c>
     </row>
     <row r="1234">
       <c r="H1234" s="1" t="n">
-        <v>714</v>
+        <v>169.33</v>
       </c>
       <c r="I1234" s="1" t="n">
-        <v>714</v>
+        <v>169.33</v>
       </c>
     </row>
     <row r="1235">
@@ -26446,8 +26446,8 @@
           <t>20000 Accounts Payable (A/P)</t>
         </is>
       </c>
-      <c r="I1268" s="1" t="n">
-        <v>722.1</v>
+      <c r="H1268" s="1" t="n">
+        <v>241.5</v>
       </c>
       <c r="J1268" t="inlineStr">
         <is>
@@ -26467,16 +26467,16 @@
           <t>10100 Checking - First Prairie</t>
         </is>
       </c>
-      <c r="H1269" s="1" t="n">
-        <v>722.1</v>
+      <c r="I1269" s="1" t="n">
+        <v>241.5</v>
       </c>
     </row>
     <row r="1270">
       <c r="H1270" s="1" t="n">
-        <v>722.1</v>
+        <v>241.5</v>
       </c>
       <c r="I1270" s="1" t="n">
-        <v>722.1</v>
+        <v>241.5</v>
       </c>
     </row>
     <row r="1271">
@@ -26627,7 +26627,7 @@
         </is>
       </c>
       <c r="H1277" s="1" t="n">
-        <v>133449.16</v>
+        <v>133425.69</v>
       </c>
       <c r="J1277" t="inlineStr">
         <is>
@@ -26648,15 +26648,15 @@
         </is>
       </c>
       <c r="I1278" s="1" t="n">
-        <v>133449.16</v>
+        <v>133425.69</v>
       </c>
     </row>
     <row r="1279">
       <c r="H1279" s="1" t="n">
-        <v>133449.16</v>
+        <v>133425.69</v>
       </c>
       <c r="I1279" s="1" t="n">
-        <v>133449.16</v>
+        <v>133425.69</v>
       </c>
     </row>
     <row r="1280">
@@ -26807,7 +26807,7 @@
         </is>
       </c>
       <c r="H1286" s="1" t="n">
-        <v>8124.9</v>
+        <v>7866.57</v>
       </c>
       <c r="J1286" t="inlineStr">
         <is>
@@ -26828,15 +26828,15 @@
         </is>
       </c>
       <c r="I1287" s="1" t="n">
-        <v>8124.9</v>
+        <v>7866.57</v>
       </c>
     </row>
     <row r="1288">
       <c r="H1288" s="1" t="n">
-        <v>8124.9</v>
+        <v>7866.57</v>
       </c>
       <c r="I1288" s="1" t="n">
-        <v>8124.9</v>
+        <v>7866.57</v>
       </c>
     </row>
     <row r="1289">
@@ -26942,7 +26942,7 @@
         </is>
       </c>
       <c r="H1293" s="1" t="n">
-        <v>7989</v>
+        <v>7730.67</v>
       </c>
       <c r="J1293" t="inlineStr">
         <is>
@@ -26967,15 +26967,15 @@
         </is>
       </c>
       <c r="I1294" s="1" t="n">
-        <v>7989</v>
+        <v>7730.67</v>
       </c>
     </row>
     <row r="1295">
       <c r="H1295" s="1" t="n">
-        <v>7989</v>
+        <v>7730.67</v>
       </c>
       <c r="I1295" s="1" t="n">
-        <v>7989</v>
+        <v>7730.67</v>
       </c>
     </row>
     <row r="1296">
@@ -27663,12 +27663,12 @@
       </c>
       <c r="F1328" t="inlineStr">
         <is>
-          <t>Shop equipment rental</t>
+          <t>Delivery equipment rental</t>
         </is>
       </c>
       <c r="G1328" t="inlineStr">
         <is>
-          <t>67000 Office Supplies</t>
+          <t>66000 Freight Out</t>
         </is>
       </c>
       <c r="H1328" s="1" t="n">
@@ -27688,7 +27688,7 @@
     <row r="1329">
       <c r="F1329" t="inlineStr">
         <is>
-          <t>Shop equipment rental</t>
+          <t>Delivery equipment rental</t>
         </is>
       </c>
       <c r="G1329" t="inlineStr">
@@ -28194,8 +28194,8 @@
           <t>67000 Office Supplies</t>
         </is>
       </c>
-      <c r="I1353" s="1" t="n">
-        <v>714</v>
+      <c r="H1353" s="1" t="n">
+        <v>169.37</v>
       </c>
       <c r="J1353" t="inlineStr">
         <is>
@@ -28219,16 +28219,16 @@
           <t>20000 Accounts Payable (A/P)</t>
         </is>
       </c>
-      <c r="H1354" s="1" t="n">
-        <v>714</v>
+      <c r="I1354" s="1" t="n">
+        <v>169.37</v>
       </c>
     </row>
     <row r="1355">
       <c r="H1355" s="1" t="n">
-        <v>714</v>
+        <v>169.37</v>
       </c>
       <c r="I1355" s="1" t="n">
-        <v>714</v>
+        <v>169.37</v>
       </c>
     </row>
     <row r="1356">
@@ -29111,7 +29111,7 @@
         </is>
       </c>
       <c r="H1399" s="1" t="n">
-        <v>7989</v>
+        <v>7730.63</v>
       </c>
       <c r="J1399" t="inlineStr">
         <is>
@@ -29136,15 +29136,15 @@
         </is>
       </c>
       <c r="I1400" s="1" t="n">
-        <v>7989</v>
+        <v>7730.63</v>
       </c>
     </row>
     <row r="1401">
       <c r="H1401" s="1" t="n">
-        <v>7989</v>
+        <v>7730.63</v>
       </c>
       <c r="I1401" s="1" t="n">
-        <v>7989</v>
+        <v>7730.63</v>
       </c>
     </row>
     <row r="1402">
@@ -30612,10 +30612,10 @@
         </is>
       </c>
       <c r="H1473" s="1" t="n">
-        <v>20426174.56</v>
+        <v>20393152.56</v>
       </c>
       <c r="I1473" s="1" t="n">
-        <v>20426174.56</v>
+        <v>20393152.56</v>
       </c>
     </row>
     <row r="1474"/>

--- a/case-studies/kestrel-valley-cycle/data/quickbooks/Journal.xlsx
+++ b/case-studies/kestrel-valley-cycle/data/quickbooks/Journal.xlsx
@@ -20560,7 +20560,7 @@
         </is>
       </c>
       <c r="H981" s="1" t="n">
-        <v>169202.82</v>
+        <v>18432.5</v>
       </c>
       <c r="J981" t="inlineStr">
         <is>
@@ -20585,15 +20585,15 @@
         </is>
       </c>
       <c r="I982" s="1" t="n">
-        <v>169202.82</v>
+        <v>18432.5</v>
       </c>
     </row>
     <row r="983">
       <c r="H983" s="1" t="n">
-        <v>169202.82</v>
+        <v>18432.5</v>
       </c>
       <c r="I983" s="1" t="n">
-        <v>169202.82</v>
+        <v>18432.5</v>
       </c>
     </row>
     <row r="984">
@@ -23229,7 +23229,7 @@
         </is>
       </c>
       <c r="H1111" s="1" t="n">
-        <v>203043.39</v>
+        <v>353813.71</v>
       </c>
       <c r="J1111" t="inlineStr">
         <is>
@@ -23254,15 +23254,15 @@
         </is>
       </c>
       <c r="I1112" s="1" t="n">
-        <v>203043.39</v>
+        <v>353813.71</v>
       </c>
     </row>
     <row r="1113">
       <c r="H1113" s="1" t="n">
-        <v>203043.39</v>
+        <v>353813.71</v>
       </c>
       <c r="I1113" s="1" t="n">
-        <v>203043.39</v>
+        <v>353813.71</v>
       </c>
     </row>
     <row r="1114">
